--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.247</t>
+    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/GlobalTile.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">???</t>
